--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T11:43:27+00:00</t>
+    <t>2026-07-01T12:03:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T12:03:19+00:00</t>
+    <t>2026-07-03T07:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -781,7 +781,7 @@
     <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-probleme-cisis|20260420150251</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-probleme-cisis|20260619134043</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -808,7 +808,7 @@
     <t>Coding of the severity with a terminology is preferred, where possible.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-severite-observation-cisis|20260420150250</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-severite-observation-cisis|20260619134042</t>
   </si>
   <si>
     <t>&lt; 272141005 |Severities|</t>
@@ -1157,7 +1157,7 @@
     <t>A simple summary of the stage such as "Stage 3". The determination of the stage is disease-specific.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-health-status-code-cisis|20260420150250</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-health-status-code-cisis|20260619134042</t>
   </si>
   <si>
     <t xml:space="preserve">con-1

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T07:33:59+00:00</t>
+    <t>2026-07-08T09:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T09:43:12+00:00</t>
+    <t>2026-07-08T10:07:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
